--- a/evaluations/classification/classification_results_color_test.xlsx
+++ b/evaluations/classification/classification_results_color_test.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S13"/>
+  <dimension ref="A1:S14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -650,25 +650,25 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BelugaID</t>
+          <t>ATRW</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6909</v>
+        <v>4325</v>
       </c>
       <c r="C4" t="n">
-        <v>747</v>
+        <v>174</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>disk</t>
+          <t>lightglue</t>
         </is>
       </c>
       <c r="E4" t="b">
         <v>0</v>
       </c>
       <c r="F4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
         <v>2</v>
@@ -691,21 +691,23 @@
       <c r="M4" t="n">
         <v>0.5</v>
       </c>
-      <c r="N4" t="inlineStr"/>
+      <c r="N4" t="n">
+        <v>5000</v>
+      </c>
       <c r="O4" t="b">
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>15.81</v>
+        <v>5.68</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0098</v>
+        <v>0.7554</v>
       </c>
       <c r="R4" t="n">
-        <v>0.0394</v>
+        <v>0.8335</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0136</v>
+        <v>0.739</v>
       </c>
     </row>
     <row r="5">
@@ -729,7 +731,7 @@
         <v>0</v>
       </c>
       <c r="F5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G5" t="n">
         <v>2</v>
@@ -757,29 +759,29 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.41</v>
+        <v>15.81</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.0164</v>
+        <v>0.0098</v>
       </c>
       <c r="R5" t="n">
-        <v>0.0402</v>
+        <v>0.0394</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0208</v>
+        <v>0.0136</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CowDataset</t>
+          <t>BelugaID</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1019</v>
+        <v>6909</v>
       </c>
       <c r="C6" t="n">
-        <v>12</v>
+        <v>747</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -790,7 +792,7 @@
         <v>0</v>
       </c>
       <c r="F6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
         <v>2</v>
@@ -818,16 +820,16 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>20.99</v>
+        <v>1.41</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.6856</v>
+        <v>0.0164</v>
       </c>
       <c r="R6" t="n">
-        <v>0.8211000000000001</v>
+        <v>0.0402</v>
       </c>
       <c r="S6" t="n">
-        <v>0.7389</v>
+        <v>0.0208</v>
       </c>
     </row>
     <row r="7">
@@ -851,7 +853,7 @@
         <v>0</v>
       </c>
       <c r="F7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7" t="n">
         <v>2</v>
@@ -879,29 +881,29 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>0.22</v>
+        <v>20.99</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.5881</v>
+        <v>0.6856</v>
       </c>
       <c r="R7" t="n">
-        <v>0.7778</v>
+        <v>0.8211000000000001</v>
       </c>
       <c r="S7" t="n">
-        <v>0.6213</v>
+        <v>0.7389</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>IPanda50</t>
+          <t>CowDataset</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5499</v>
+        <v>1019</v>
       </c>
       <c r="C8" t="n">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -912,7 +914,7 @@
         <v>0</v>
       </c>
       <c r="F8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
         <v>2</v>
@@ -940,16 +942,16 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>16.01</v>
+        <v>0.22</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.0274</v>
+        <v>0.5881</v>
       </c>
       <c r="R8" t="n">
-        <v>0.1155</v>
+        <v>0.7778</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0015</v>
+        <v>0.6213</v>
       </c>
     </row>
     <row r="9">
@@ -973,7 +975,7 @@
         <v>0</v>
       </c>
       <c r="F9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G9" t="n">
         <v>2</v>
@@ -1001,29 +1003,29 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.1</v>
+        <v>16.01</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.5714</v>
+        <v>0.0274</v>
       </c>
       <c r="R9" t="n">
-        <v>0.7528</v>
+        <v>0.1155</v>
       </c>
       <c r="S9" t="n">
-        <v>0.5653</v>
+        <v>0.0015</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>NyalaData</t>
+          <t>IPanda50</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1498</v>
+        <v>5499</v>
       </c>
       <c r="C10" t="n">
-        <v>227</v>
+        <v>48</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1034,7 +1036,7 @@
         <v>0</v>
       </c>
       <c r="F10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
         <v>2</v>
@@ -1062,16 +1064,16 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>7.67</v>
+        <v>1.1</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.0751</v>
+        <v>0.5714</v>
       </c>
       <c r="R10" t="n">
-        <v>0.2283</v>
+        <v>0.7528</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0654</v>
+        <v>0.5653</v>
       </c>
     </row>
     <row r="11">
@@ -1095,7 +1097,7 @@
         <v>0</v>
       </c>
       <c r="F11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G11" t="n">
         <v>2</v>
@@ -1123,29 +1125,29 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>0.27</v>
+        <v>7.67</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.0549</v>
+        <v>0.0751</v>
       </c>
       <c r="R11" t="n">
-        <v>0.1474</v>
+        <v>0.2283</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0434</v>
+        <v>0.0654</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SealID</t>
+          <t>NyalaData</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1668</v>
+        <v>1498</v>
       </c>
       <c r="C12" t="n">
-        <v>55</v>
+        <v>227</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1156,7 +1158,7 @@
         <v>0</v>
       </c>
       <c r="F12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
         <v>2</v>
@@ -1184,16 +1186,16 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>8.67</v>
+        <v>0.27</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.0399</v>
+        <v>0.0549</v>
       </c>
       <c r="R12" t="n">
-        <v>0.1661</v>
+        <v>0.1474</v>
       </c>
       <c r="S12" t="n">
-        <v>0.0031</v>
+        <v>0.0434</v>
       </c>
     </row>
     <row r="13">
@@ -1217,7 +1219,7 @@
         <v>0</v>
       </c>
       <c r="F13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G13" t="n">
         <v>2</v>
@@ -1245,15 +1247,76 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
+        <v>8.67</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.0399</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.1661</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.0031</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>SealID</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1668</v>
+      </c>
+      <c r="C14" t="n">
+        <v>55</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>disk</t>
+        </is>
+      </c>
+      <c r="E14" t="b">
+        <v>0</v>
+      </c>
+      <c r="F14" t="b">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2</v>
+      </c>
+      <c r="H14" t="n">
+        <v>128</v>
+      </c>
+      <c r="I14" t="b">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="K14" t="n">
+        <v>20</v>
+      </c>
+      <c r="L14" t="n">
+        <v>10</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="b">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
         <v>0.28</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="Q14" t="n">
         <v>0.5083</v>
       </c>
-      <c r="R13" t="n">
+      <c r="R14" t="n">
         <v>0.6977</v>
       </c>
-      <c r="S13" t="n">
+      <c r="S14" t="n">
         <v>0.4933</v>
       </c>
     </row>
